--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-17.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-17.xlsx
@@ -368,6 +368,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-17.xlsx
+++ b/paper_traning_lay0x0/sinais_lay0x0_gestao_2026-07-17.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/paper_traning_lay0x0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_6E395F915769E6737B5A3311595ED87656CD1882" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{412CB099-EE28-4BDC-BAAB-D3C20E29FBF5}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_6E395F915769E6737B5A3311595ED87656CD1882" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8969A002-CAAA-4914-AF99-441BCB2E4C10}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sinais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -659,10 +672,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -700,7 +713,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -728,14 +741,18 @@
       <c r="I2">
         <v>15.38</v>
       </c>
+      <c r="J2" t="str">
+        <f>IF(M2=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
+      </c>
       <c r="L2" t="s">
         <v>18</v>
       </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -763,14 +780,18 @@
       <c r="I3">
         <v>12.5</v>
       </c>
+      <c r="J3" t="str">
+        <f t="shared" ref="J3:J21" si="0">IF(M3=1,"GREEN", "RED")</f>
+        <v>GREEN</v>
+      </c>
       <c r="L3" t="s">
         <v>18</v>
       </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -798,14 +819,18 @@
       <c r="I4">
         <v>11.76</v>
       </c>
+      <c r="J4" t="str">
+        <f t="shared" si="0"/>
+        <v>RED</v>
+      </c>
       <c r="L4" t="s">
         <v>18</v>
       </c>
-      <c r="N4">
+      <c r="M4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -833,14 +858,18 @@
       <c r="I5">
         <v>16.670000000000002</v>
       </c>
+      <c r="J5" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L5" t="s">
         <v>18</v>
       </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -868,14 +897,18 @@
       <c r="I6">
         <v>4.6500000000000004</v>
       </c>
+      <c r="J6" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L6" t="s">
         <v>18</v>
       </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -903,14 +936,18 @@
       <c r="I7">
         <v>18.18</v>
       </c>
+      <c r="J7" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L7" t="s">
         <v>18</v>
       </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -938,14 +975,18 @@
       <c r="I8">
         <v>14.29</v>
       </c>
+      <c r="J8" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L8" t="s">
         <v>18</v>
       </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -973,14 +1014,18 @@
       <c r="I9">
         <v>9.52</v>
       </c>
+      <c r="J9" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L9" t="s">
         <v>18</v>
       </c>
-      <c r="N9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -1008,14 +1053,18 @@
       <c r="I10">
         <v>10</v>
       </c>
+      <c r="J10" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L10" t="s">
         <v>18</v>
       </c>
-      <c r="N10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1043,14 +1092,18 @@
       <c r="I11">
         <v>12.5</v>
       </c>
+      <c r="J11" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L11" t="s">
         <v>18</v>
       </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1078,14 +1131,18 @@
       <c r="I12">
         <v>9.52</v>
       </c>
+      <c r="J12" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L12" t="s">
         <v>18</v>
       </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -1113,14 +1170,18 @@
       <c r="I13">
         <v>20</v>
       </c>
+      <c r="J13" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L13" t="s">
         <v>18</v>
       </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1148,14 +1209,18 @@
       <c r="I14">
         <v>10</v>
       </c>
+      <c r="J14" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L14" t="s">
         <v>18</v>
       </c>
-      <c r="N14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1183,14 +1248,18 @@
       <c r="I15">
         <v>12.5</v>
       </c>
+      <c r="J15" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L15" t="s">
         <v>18</v>
       </c>
-      <c r="N15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -1218,14 +1287,18 @@
       <c r="I16">
         <v>17.39</v>
       </c>
+      <c r="J16" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L16" t="s">
         <v>18</v>
       </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -1253,14 +1326,18 @@
       <c r="I17">
         <v>19.05</v>
       </c>
+      <c r="J17" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L17" t="s">
         <v>18</v>
       </c>
-      <c r="N17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -1288,14 +1365,18 @@
       <c r="I18">
         <v>20</v>
       </c>
+      <c r="J18" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L18" t="s">
         <v>18</v>
       </c>
-      <c r="N18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -1323,14 +1404,18 @@
       <c r="I19">
         <v>10</v>
       </c>
+      <c r="J19" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L19" t="s">
         <v>18</v>
       </c>
-      <c r="N19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -1358,14 +1443,18 @@
       <c r="I20">
         <v>9.52</v>
       </c>
+      <c r="J20" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L20" t="s">
         <v>18</v>
       </c>
-      <c r="N20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -1393,10 +1482,14 @@
       <c r="I21">
         <v>8</v>
       </c>
+      <c r="J21" t="str">
+        <f t="shared" si="0"/>
+        <v>GREEN</v>
+      </c>
       <c r="L21" t="s">
         <v>18</v>
       </c>
-      <c r="N21">
+      <c r="M21">
         <v>1</v>
       </c>
     </row>
